--- a/inventories/baseline/lci-East-Taijinar.xlsx
+++ b/inventories/baseline/lci-East-Taijinar.xlsx
@@ -850,7 +850,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>0.7688046629033869</v>
+        <v>1.025072883871182</v>
       </c>
       <c r="C28" t="s">
         <v>1</v>
@@ -867,7 +867,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>0.1842461375197011</v>
+        <v>0.2296347666929349</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>22</v>
       </c>
       <c r="B31">
-        <v>0.001306682140093078</v>
+        <v>0.001495997056790771</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
@@ -1348,7 +1348,7 @@
         <v>3</v>
       </c>
       <c r="B73">
-        <v>0.0005860508005212914</v>
+        <v>0.0005860508005212913</v>
       </c>
       <c r="C73" t="s">
         <v>1</v>
@@ -2489,7 +2489,7 @@
         <v>54</v>
       </c>
       <c r="B182">
-        <v>0.0008306451612903225</v>
+        <v>0.0008306451612903227</v>
       </c>
       <c r="D182" t="s">
         <v>11</v>
@@ -2659,7 +2659,7 @@
         <v>63</v>
       </c>
       <c r="B192">
-        <v>8.999999999999999E-05</v>
+        <v>9.000000000000001E-05</v>
       </c>
       <c r="C192" t="s">
         <v>31</v>
@@ -3357,7 +3357,7 @@
         <v>48</v>
       </c>
       <c r="B254">
-        <v>0.9474247108642541</v>
+        <v>0.9474247108642542</v>
       </c>
       <c r="C254" t="s">
         <v>1</v>
@@ -3391,7 +3391,7 @@
         <v>32</v>
       </c>
       <c r="B256">
-        <v>-0.01882166098173361</v>
+        <v>-0.01882166098173362</v>
       </c>
       <c r="C256" t="s">
         <v>31</v>
